--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -23,9 +23,27 @@
     <x:t>FName</x:t>
   </x:si>
   <x:si>
+    <x:t>John</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hank</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dagny</x:t>
+  </x:si>
+  <x:si>
     <x:t>LName</x:t>
   </x:si>
   <x:si>
+    <x:t>Galt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rearden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Taggart</x:t>
+  </x:si>
+  <x:si>
     <x:t>Outcast</x:t>
   </x:si>
   <x:si>
@@ -33,24 +51,6 @@
   </x:si>
   <x:si>
     <x:t>Income</x:t>
-  </x:si>
-  <x:si>
-    <x:t>John</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Galt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hank</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rearden</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dagny</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Taggart</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -696,24 +696,24 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="B4" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="8" t="b">
         <x:v>1</x:v>
@@ -727,10 +727,10 @@
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="B5" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D5" s="8" t="b">
         <x:v>0</x:v>
@@ -744,10 +744,10 @@
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="B6" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="12" t="b">
         <x:v>0</x:v>
@@ -793,24 +793,24 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E2" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="7" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="8" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="B3" s="8" t="s">
-        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="8" t="b">
         <x:v>1</x:v>
@@ -824,10 +824,10 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C4" s="8" t="b">
         <x:v>0</x:v>
@@ -841,10 +841,10 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="12" t="b">
         <x:v>0</x:v>

--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -668,18 +668,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="7.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
@@ -763,19 +760,12 @@
   <x:mergeCells count="1">
     <x:mergeCell ref="B2:F2"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -860,10 +850,6 @@
   <x:mergeCells count="1">
     <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -672,11 +672,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="8.567768" customWidth="1"/>
-    <x:col min="4" max="4" width="8.139196" customWidth="1"/>
-    <x:col min="5" max="5" width="10.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="8.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
+    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
+    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
+    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CopyingRanges.xlsx
@@ -671,12 +671,12 @@
   <x:dimension ref="A1:F6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="7.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="8.282054" customWidth="1"/>
-    <x:col min="4" max="4" width="7.853482" customWidth="1"/>
-    <x:col min="5" max="5" width="9.853482" customWidth="1"/>
-    <x:col min="6" max="6" width="8.424911" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="7.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="8.285714" customWidth="1"/>
+    <x:col min="4" max="4" width="7.857143" customWidth="1"/>
+    <x:col min="5" max="5" width="9.857143" customWidth="1"/>
+    <x:col min="6" max="6" width="8.428571" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">
